--- a/cr_tree_diag_gen/examples/input/sub_clock_table.xlsx
+++ b/cr_tree_diag_gen/examples/input/sub_clock_table.xlsx
@@ -1218,12 +1218,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="29.6346153846154" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="15.3846153846154" customWidth="1"/>
     <col min="2" max="2" width="5.19230769230769" customWidth="1"/>
     <col min="3" max="3" width="12.1153846153846" customWidth="1"/>
-    <col min="4" max="4" width="10.5769230769231" customWidth="1"/>
+    <col min="4" max="4" width="14.5769230769231" customWidth="1"/>
     <col min="5" max="5" width="12.6923076923077" customWidth="1"/>
     <col min="6" max="6" width="10.7692307692308" customWidth="1"/>
     <col min="7" max="7" width="12.8846153846154" customWidth="1"/>
@@ -1233,6 +1233,7 @@
     <col min="11" max="11" width="11.3461538461538" customWidth="1"/>
     <col min="12" max="12" width="7.88461538461539" customWidth="1"/>
     <col min="13" max="13" width="10.1923076923077" customWidth="1"/>
+    <col min="14" max="16384" width="29.6346153846154" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:13">
